--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>170654</v>
+        <v>171260.59375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>167.559998</v>
+        <v>168.350006</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>105.550003</v>
+        <v>105.809998</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>433.700012</v>
+        <v>435.450012</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1431</v>
+        <v>5.1453</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8966</v>
+        <v>5.8964</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7482.709961</v>
+        <v>7492.100098</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25870.650391</v>
+        <v>25918.525391</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52348.390625</v>
+        <v>52299.730469</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4125.299805</v>
+        <v>4133.700195</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>73.989998</v>
+        <v>73.129997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>78.650002</v>
+        <v>77.910004</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1187.5</v>
+        <v>1185.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>451</v>
+        <v>451.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>171260.59375</v>
+        <v>172742</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>168.350006</v>
+        <v>169.800003</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>105.809998</v>
+        <v>107.760002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>435.450012</v>
+        <v>435.079987</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1453</v>
+        <v>5.1146</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8964</v>
+        <v>5.8474</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7492.100098</v>
+        <v>7543.640137</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25918.525391</v>
+        <v>26206.890625</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52299.730469</v>
+        <v>52487.410156</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4133.700195</v>
+        <v>4117.700195</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>73.129997</v>
+        <v>71.949997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>77.910004</v>
+        <v>76.360001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1185.5</v>
+        <v>1180.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>451.5</v>
+        <v>451.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>172742</v>
+        <v>177866</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>169.800003</v>
+        <v>175.009995</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>107.760002</v>
+        <v>111.080002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>435.079987</v>
+        <v>436.290009</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1146</v>
+        <v>5.1075</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8474</v>
+        <v>5.8296</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7543.640137</v>
+        <v>7575.390137</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>26206.890625</v>
+        <v>26281.609375</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52487.410156</v>
+        <v>52637.011719</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4117.700195</v>
+        <v>4104.100098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>71.949997</v>
+        <v>71.410004</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>76.360001</v>
+        <v>76.010002</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1180.25</v>
+        <v>1196.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>451.75</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4104.100098</v>
+        <v>4113.700195</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1196.5</v>
+        <v>1190.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>438</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1075</v>
+        <v>5.1165</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8296</v>
+        <v>5.8455</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4113.700195</v>
+        <v>4067.899902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>71.410004</v>
+        <v>74.129997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>76.010002</v>
+        <v>78.879997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1190.75</v>
+        <v>1196.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>461</v>
+        <v>467.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>177866</v>
+        <v>175739</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>175.009995</v>
+        <v>172.25</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>111.080002</v>
+        <v>109.199997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>436.290009</v>
+        <v>434.600006</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1165</v>
+        <v>5.1318</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8455</v>
+        <v>5.8466</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7575.390137</v>
+        <v>7515.339844</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>26281.609375</v>
+        <v>25873.179688</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52637.011719</v>
+        <v>52498.640625</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4067.899902</v>
+        <v>4029</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>74.129997</v>
+        <v>80.510002</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>78.879997</v>
+        <v>86.900002</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1196.25</v>
+        <v>1187.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>467.25</v>
+        <v>457.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>172.25</v>
+        <v>173.600006</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>109.199997</v>
+        <v>110.400002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>434.600006</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1318</v>
+        <v>5.0745</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8466</v>
+        <v>5.7922</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4029</v>
+        <v>4035.899902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>80.510002</v>
+        <v>79.81999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>86.900002</v>
+        <v>85.260002</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1187.5</v>
+        <v>1195.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>457.5</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>175739</v>
+        <v>175690.03125</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>173.600006</v>
+        <v>172.649994</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>110.400002</v>
+        <v>109.639999</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>432</v>
+        <v>432.140015</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0745</v>
+        <v>5.0804</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7922</v>
+        <v>5.8103</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7515.339844</v>
+        <v>7533.77002</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25873.179688</v>
+        <v>26095.494141</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52498.640625</v>
+        <v>52471</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4035.899902</v>
+        <v>4041.800049</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>79.81999999999999</v>
+        <v>79.040001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>85.260002</v>
+        <v>84.449997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1195.5</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>175690.03125</v>
+        <v>176011</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>172.649994</v>
+        <v>172.759995</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>109.639999</v>
+        <v>109.690002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>432.140015</v>
+        <v>433.399994</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0804</v>
+        <v>5.0761</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8103</v>
+        <v>5.8178</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7533.77002</v>
+        <v>7572.399902</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>26095.494141</v>
+        <v>26269.230469</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52471</v>
+        <v>52658.640625</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4041.800049</v>
+        <v>4029.300049</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>79.040001</v>
+        <v>79.489998</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>84.449997</v>
+        <v>84.660004</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1195</v>
+        <v>1204.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>176011</v>
+        <v>173825</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>172.759995</v>
+        <v>170.770004</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>109.690002</v>
+        <v>108.419998</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>433.399994</v>
+        <v>433.040009</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0761</v>
+        <v>5.1028</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8178</v>
+        <v>5.8311</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7572.399902</v>
+        <v>7533.77002</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>26269.230469</v>
+        <v>25881.949219</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52658.640625</v>
+        <v>52552.96875</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4029.300049</v>
+        <v>3995.699951</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>79.489998</v>
+        <v>80.139999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>84.660004</v>
+        <v>85.949997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1204.5</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>471</v>
+        <v>463.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>173825</v>
+        <v>173714</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>170.770004</v>
+        <v>170.630005</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>108.419998</v>
+        <v>107.43</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>433.040009</v>
+        <v>429.119995</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1028</v>
+        <v>5.1108</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8311</v>
+        <v>5.8439</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7533.77002</v>
+        <v>7457.689941</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25881.949219</v>
+        <v>25520.240234</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52552.96875</v>
+        <v>52146.421875</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>3995.699951</v>
+        <v>4012.699951</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>80.139999</v>
+        <v>82.489998</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>85.949997</v>
+        <v>88.099998</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1195</v>
+        <v>1204.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>463.5</v>
+        <v>444.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4012.699951</v>
+        <v>4018.800049</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>82.489998</v>
+        <v>81.779999</v>
       </c>
     </row>
     <row r="13">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1204.5</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>444.75</v>
+        <v>467.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1108</v>
+        <v>5.1072</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8439</v>
+        <v>5.8329</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4018.800049</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>81.779999</v>
+        <v>81.400002</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>88.099998</v>
+        <v>88.220001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1203</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>467.5</v>
+        <v>475.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>173714</v>
+        <v>173371</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>170.630005</v>
+        <v>170.300003</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>107.43</v>
+        <v>106.230003</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>429.119995</v>
+        <v>426.970001</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1072</v>
+        <v>5.0921</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8329</v>
+        <v>5.8157</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7457.689941</v>
+        <v>7443.279785</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25520.240234</v>
+        <v>25508.070312</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52146.421875</v>
+        <v>51839.261719</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4020</v>
+        <v>4064.800049</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>81.400002</v>
+        <v>83.620003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>88.220001</v>
+        <v>90.400002</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1220</v>
+        <v>1226.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>475.25</v>
+        <v>471.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>173371</v>
+        <v>173326</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>170.300003</v>
+        <v>170.339996</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>106.230003</v>
+        <v>105.949997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>426.970001</v>
+        <v>430.109985</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0921</v>
+        <v>5.072</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8157</v>
+        <v>5.7838</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7443.279785</v>
+        <v>7509.200195</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25508.070312</v>
+        <v>25837.210938</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>51839.261719</v>
+        <v>52224.640625</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4064.800049</v>
+        <v>4122.799805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>83.620003</v>
+        <v>87.129997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>90.400002</v>
+        <v>84.800003</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1226.5</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>471.5</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>173326</v>
+        <v>177548</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>170.339996</v>
+        <v>174.699997</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>105.949997</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>430.109985</v>
+        <v>428.859985</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.072</v>
+        <v>5.0572</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7838</v>
+        <v>5.7601</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7509.200195</v>
+        <v>7498.959961</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25837.210938</v>
+        <v>25690.900391</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52224.640625</v>
+        <v>52218.578125</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4122.799805</v>
+        <v>4077.899902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>87.129997</v>
+        <v>91.06999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>84.800003</v>
+        <v>93.30999799999999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1227</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>481</v>
+        <v>488.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>177548</v>
+        <v>176724</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>174.699997</v>
+        <v>173.449997</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>107.5</v>
+        <v>106.18</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>428.859985</v>
+        <v>425.519989</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0572</v>
+        <v>5.0821</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7601</v>
+        <v>5.7826</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7498.959961</v>
+        <v>7408.299805</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25690.900391</v>
+        <v>25137.689453</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52218.578125</v>
+        <v>51711.648438</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4077.899902</v>
+        <v>4062.100098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>91.06999999999999</v>
+        <v>89.879997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>93.30999799999999</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1244</v>
+        <v>1247.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>488.75</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>176724</v>
+        <v>174042</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>173.449997</v>
+        <v>170.949997</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>106.18</v>
+        <v>105.050003</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>425.519989</v>
+        <v>425.049988</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0821</v>
+        <v>5.0751</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7826</v>
+        <v>5.7816</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7408.299805</v>
+        <v>7411.97998</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25137.689453</v>
+        <v>24975.820312</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>51711.648438</v>
+        <v>51947.25</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4062.100098</v>
+        <v>4067.600098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>89.879997</v>
+        <v>89.30999799999999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>92</v>
+        <v>96.779999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1247.5</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>487</v>
+        <v>464.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>174042</v>
+        <v>176724</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7411.97998</v>
+        <v>7408.299805</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>24975.820312</v>
+        <v>25137.689453</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>51947.25</v>
+        <v>51711.648438</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4067.600098</v>
+        <v>4070.800049</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1248</v>
+        <v>1253.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>464.25</v>
+        <v>487.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0751</v>
+        <v>5.0846</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7816</v>
+        <v>5.7877</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4070.800049</v>
+        <v>4089.899902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>89.30999799999999</v>
+        <v>83.93000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>96.779999</v>
+        <v>90.550003</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1253.5</v>
+        <v>1220.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>487.25</v>
+        <v>473.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>176724</v>
+        <v>175335</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>170.949997</v>
+        <v>172.75</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>105.050003</v>
+        <v>106.699997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>425.049988</v>
+        <v>426.859985</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0846</v>
+        <v>5.1097</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7877</v>
+        <v>5.8091</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7408.299805</v>
+        <v>7413.180176</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>25137.689453</v>
+        <v>24932.080078</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>51711.648438</v>
+        <v>52210.078125</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4089.899902</v>
+        <v>4026.600098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>83.93000000000001</v>
+        <v>81.860001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>90.550003</v>
+        <v>87.160004</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1220.25</v>
+        <v>1208.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>473.75</v>
+        <v>475.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>172.75</v>
+        <v>173.740005</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>106.699997</v>
+        <v>107.169998</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>426.859985</v>
+        <v>428.609985</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1097</v>
+        <v>5.1259</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8091</v>
+        <v>5.8325</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7413.180176</v>
+        <v>7428.779785</v>
       </c>
     </row>
     <row r="9">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4026.600098</v>
+        <v>4092.399902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>81.860001</v>
+        <v>82.660004</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>87.160004</v>
+        <v>87.91999800000001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1208.5</v>
+        <v>1207.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>475.75</v>
+        <v>478.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>175335</v>
+        <v>173885</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>173.740005</v>
+        <v>170.550003</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>107.169998</v>
+        <v>105.099998</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>428.609985</v>
+        <v>421.559998</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.0804</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1259</v>
+        <v>5.099</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8325</v>
+        <v>5.8475</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4395.259766</v>
       </c>
       <c r="F8" t="n">
-        <v>7428.779785</v>
+        <v>7316.149902</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14672.679688</v>
       </c>
       <c r="F9" t="n">
-        <v>24932.080078</v>
+        <v>24442.939453</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>34935.46875</v>
       </c>
       <c r="F10" t="n">
-        <v>52210.078125</v>
+        <v>51594.140625</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1812.599976</v>
       </c>
       <c r="F11" t="n">
-        <v>4092.399902</v>
+        <v>4136.799805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>73.949997</v>
       </c>
       <c r="F12" t="n">
-        <v>82.660004</v>
+        <v>83.41999800000001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>76.33000199999999</v>
       </c>
       <c r="F13" t="n">
-        <v>87.91999800000001</v>
+        <v>89.889999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1414.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1207.75</v>
+        <v>1193.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>478.5</v>
+        <v>473.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>121801</v>
       </c>
       <c r="F2" t="n">
-        <v>173885</v>
+        <v>177159</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>117.110001</v>
       </c>
       <c r="F3" t="n">
-        <v>170.550003</v>
+        <v>174.309998</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>141.800003</v>
       </c>
       <c r="F4" t="n">
-        <v>105.099998</v>
+        <v>107.360001</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>250.350006</v>
       </c>
       <c r="F5" t="n">
-        <v>421.559998</v>
+        <v>425.369995</v>
       </c>
     </row>
     <row r="6">
@@ -547,19 +547,19 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0804</v>
+        <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.099</v>
+        <v>5.0716</v>
       </c>
     </row>
     <row r="7">
@@ -569,19 +569,19 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0387</v>
+        <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8475</v>
+        <v>5.8255</v>
       </c>
     </row>
     <row r="8">
@@ -591,19 +591,19 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
-        <v>4395.259766</v>
+        <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7316.149902</v>
+        <v>7437.629883</v>
       </c>
     </row>
     <row r="9">
@@ -613,19 +613,19 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
-        <v>14672.679688</v>
+        <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>24442.939453</v>
+        <v>25122.179688</v>
       </c>
     </row>
     <row r="10">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>34935.46875</v>
+        <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>51594.140625</v>
+        <v>52208.058594</v>
       </c>
     </row>
     <row r="11">
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>1812.599976</v>
+        <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4136.799805</v>
+        <v>4109.799805</v>
       </c>
     </row>
     <row r="12">
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>73.949997</v>
+        <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.41999800000001</v>
+        <v>84.839996</v>
       </c>
     </row>
     <row r="13">
@@ -701,19 +701,19 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>76.33000199999999</v>
+        <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>89.889999</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="14">
@@ -723,19 +723,19 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>1414.75</v>
+        <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1193.25</v>
+        <v>1188.5</v>
       </c>
     </row>
     <row r="15">
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>473.5</v>
+        <v>466.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -459,19 +459,19 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" t="n">
-        <v>121801</v>
+        <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>177159</v>
+        <v>177999</v>
       </c>
     </row>
     <row r="3">
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>117.110001</v>
+        <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>174.309998</v>
+        <v>175.020004</v>
       </c>
     </row>
     <row r="4">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>141.800003</v>
+        <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>107.360001</v>
+        <v>107.25</v>
       </c>
     </row>
     <row r="5">
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>250.350006</v>
+        <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>425.369995</v>
+        <v>428.390015</v>
       </c>
     </row>
     <row r="6">
@@ -550,16 +550,16 @@
         <v>44439</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0716</v>
+        <v>5.0747</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8255</v>
+        <v>5.8536</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7437.629883</v>
+        <v>7489.720215</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>25122.179688</v>
+        <v>25373.849609</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>52208.058594</v>
+        <v>52485.03125</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4109.799805</v>
+        <v>4049.100098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>84.839996</v>
+        <v>84.66999800000001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>90.25</v>
+        <v>90.120003</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1188.5</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>466.25</v>
+        <v>440.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4049.100098</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1172</v>
+        <v>1187.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>440.75</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0747</v>
+        <v>5.0598</v>
       </c>
     </row>
     <row r="7">
@@ -572,16 +572,16 @@
         <v>44439</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8536</v>
+        <v>5.8308</v>
       </c>
     </row>
     <row r="8">
@@ -660,16 +660,16 @@
         <v>44439</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4107</v>
+        <v>4101.899902</v>
       </c>
     </row>
     <row r="12">
@@ -682,16 +682,16 @@
         <v>44439</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>84.66999800000001</v>
+        <v>78.849998</v>
       </c>
     </row>
     <row r="13">
@@ -704,16 +704,16 @@
         <v>44439</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E13" t="n">
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>90.120003</v>
+        <v>82.839996</v>
       </c>
     </row>
     <row r="14">
@@ -726,16 +726,16 @@
         <v>44439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" t="n">
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1187.5</v>
+        <v>1179.75</v>
       </c>
     </row>
     <row r="15">
@@ -748,16 +748,16 @@
         <v>44439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15" t="n">
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>464</v>
+        <v>461.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -462,16 +462,16 @@
         <v>44439</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>177999</v>
+        <v>178000</v>
       </c>
     </row>
     <row r="3">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0598</v>
+        <v>5.0743</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8308</v>
+        <v>5.8596</v>
       </c>
     </row>
     <row r="8">
@@ -594,16 +594,16 @@
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D8" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7489.720215</v>
+        <v>7600.5</v>
       </c>
     </row>
     <row r="9">
@@ -612,21 +612,13 @@
           <t>nasdaq</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>46234</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>60</v>
-      </c>
-      <c r="E9" t="n">
-        <v>15259.240234</v>
-      </c>
-      <c r="F9" t="n">
-        <v>25373.849609</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -638,16 +630,16 @@
         <v>44439</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>52485.03125</v>
+        <v>53178.410156</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +661,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4101.899902</v>
+        <v>4133.799805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +683,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>78.849998</v>
+        <v>77.480003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +705,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>82.839996</v>
+        <v>81.370003</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +727,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1179.75</v>
+        <v>1182.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +749,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>461.5</v>
+        <v>469.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>178000</v>
+        <v>177895</v>
       </c>
     </row>
     <row r="3">
@@ -484,16 +484,16 @@
         <v>44439</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>175.020004</v>
+        <v>174.899994</v>
       </c>
     </row>
     <row r="4">
@@ -506,16 +506,16 @@
         <v>44439</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>107.25</v>
+        <v>108.379997</v>
       </c>
     </row>
     <row r="5">
@@ -528,16 +528,16 @@
         <v>44439</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>428.390015</v>
+        <v>435.829987</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0743</v>
+        <v>5.1397</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8596</v>
+        <v>5.9358</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7600.5</v>
+        <v>7736.52002</v>
       </c>
     </row>
     <row r="9">
@@ -612,13 +612,21 @@
           <t>nasdaq</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="B9" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>46265</v>
+      </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15259.240234</v>
+      </c>
+      <c r="F9" t="n">
+        <v>26584.990234</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -639,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53178.410156</v>
+        <v>54085.878906</v>
       </c>
     </row>
     <row r="11">
@@ -661,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4133.799805</v>
+        <v>4246.5</v>
       </c>
     </row>
     <row r="12">
@@ -683,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>77.480003</v>
+        <v>76.19000200000001</v>
       </c>
     </row>
     <row r="13">
@@ -705,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>81.370003</v>
+        <v>80.279999</v>
       </c>
     </row>
     <row r="14">
@@ -727,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1182.25</v>
+        <v>1167.75</v>
       </c>
     </row>
     <row r="15">
@@ -749,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>469.25</v>
+        <v>459.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>177895</v>
+        <v>177726</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>174.899994</v>
+        <v>174.699997</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>108.379997</v>
+        <v>107.790001</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>435.829987</v>
+        <v>446.51001</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1397</v>
+        <v>5.1165</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9358</v>
+        <v>5.9151</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7736.52002</v>
+        <v>7723.549805</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26584.990234</v>
+        <v>26363.439453</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>54085.878906</v>
+        <v>54349.121094</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4246.5</v>
+        <v>4312.799805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>76.19000200000001</v>
+        <v>76.129997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>80.279999</v>
+        <v>80.55999799999999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1167.75</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>459.25</v>
+        <v>460.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>177726</v>
+        <v>175546</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>174.699997</v>
+        <v>172.039993</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>107.790001</v>
+        <v>105.910004</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>446.51001</v>
+        <v>443.950012</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1165</v>
+        <v>5.1014</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9151</v>
+        <v>5.8811</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7723.549805</v>
+        <v>7709.959961</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26363.439453</v>
+        <v>26348.349609</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>54349.121094</v>
+        <v>53885.101562</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4312.799805</v>
+        <v>4375.799805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>76.129997</v>
+        <v>76.879997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>80.55999799999999</v>
+        <v>81.839996</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1174</v>
+        <v>1182.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>460.5</v>
+        <v>465.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>175546</v>
+        <v>172513</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>172.039993</v>
+        <v>169.369995</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>105.910004</v>
+        <v>104.699997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>443.950012</v>
+        <v>444.350006</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1014</v>
+        <v>5.0842</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8811</v>
+        <v>5.8734</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7709.959961</v>
+        <v>7757.640137</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26348.349609</v>
+        <v>26690.619141</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53885.101562</v>
+        <v>54036.929688</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4375.799805</v>
+        <v>4340.700195</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>76.879997</v>
+        <v>78.18000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>81.839996</v>
+        <v>83.550003</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1182.25</v>
+        <v>1156.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>465.25</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4340.700195</v>
+        <v>4399.700195</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1156.5</v>
+        <v>1176.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>439</v>
+        <v>461.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0842</v>
+        <v>5.0848</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8734</v>
+        <v>5.8753</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4399.700195</v>
+        <v>4395.700195</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>78.18000000000001</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>83.550003</v>
+        <v>84.949997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1176.25</v>
+        <v>1183.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>461.5</v>
+        <v>463.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>172513</v>
+        <v>172180</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>169.369995</v>
+        <v>169.270004</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>104.699997</v>
+        <v>103.519997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>444.350006</v>
+        <v>446.850006</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0848</v>
+        <v>5.1133</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8753</v>
+        <v>5.8987</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7757.640137</v>
+        <v>7753.109863</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26690.619141</v>
+        <v>26605.359375</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>54036.929688</v>
+        <v>53975.980469</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4395.700195</v>
+        <v>4436.600098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>79.5</v>
+        <v>83.68000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>84.949997</v>
+        <v>89.19000200000001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1183.25</v>
+        <v>1180.75</v>
       </c>
     </row>
     <row r="15">

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>172180</v>
+        <v>167875</v>
       </c>
     </row>
     <row r="3">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1133</v>
+        <v>5.1716</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8987</v>
+        <v>5.9654</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7753.109863</v>
+        <v>7728.200195</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26605.359375</v>
+        <v>26445.449219</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53975.980469</v>
+        <v>53791.851562</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4436.600098</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.68000000000001</v>
+        <v>83.519997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>89.19000200000001</v>
+        <v>89.220001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1180.75</v>
+        <v>1175.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>463.75</v>
+        <v>465.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>167875</v>
+        <v>167491</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>169.270004</v>
+        <v>165.050003</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>103.519997</v>
+        <v>101.199997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>446.850006</v>
+        <v>450.350006</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1716</v>
+        <v>5.1612</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9654</v>
+        <v>5.9514</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7728.200195</v>
+        <v>7748.5</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26445.449219</v>
+        <v>26588.490234</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53791.851562</v>
+        <v>53770.269531</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4469</v>
+        <v>4450.399902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.519997</v>
+        <v>81.459999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>89.220001</v>
+        <v>87.220001</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1175.25</v>
+        <v>1184.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>465.75</v>
+        <v>478.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>167491</v>
+        <v>167101</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>165.050003</v>
+        <v>164.669998</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>101.199997</v>
+        <v>100.769997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>450.350006</v>
+        <v>452.440002</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1612</v>
+        <v>5.189</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9514</v>
+        <v>5.9962</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7748.5</v>
+        <v>7798.990234</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26588.490234</v>
+        <v>26803.029297</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53770.269531</v>
+        <v>53839.988281</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4450.399902</v>
+        <v>4407.899902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>81.459999</v>
+        <v>81.699997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>87.220001</v>
+        <v>87.160004</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1184.5</v>
+        <v>1186.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>478.25</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>167101</v>
+        <v>166934</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>164.669998</v>
+        <v>164.149994</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>100.769997</v>
+        <v>100.970001</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>452.440002</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.189</v>
+        <v>5.2132</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9962</v>
+        <v>6.0459</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7798.990234</v>
+        <v>7785.759766</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26803.029297</v>
+        <v>26729.160156</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53839.988281</v>
+        <v>53732.410156</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4407.899902</v>
+        <v>4380.399902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>81.699997</v>
+        <v>82.400002</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>87.160004</v>
+        <v>88.519997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1186.5</v>
+        <v>1173.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>476</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>164.149994</v>
+        <v>163.899994</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>100.970001</v>
+        <v>100.120003</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>457</v>
+        <v>458.100006</v>
       </c>
     </row>
     <row r="6">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4380.399902</v>
+        <v>4437.299805</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1173.75</v>
+        <v>1192.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>459</v>
+        <v>483.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2132</v>
+        <v>5.2265</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0459</v>
+        <v>6.0614</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4437.299805</v>
+        <v>4452.100098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>82.400002</v>
+        <v>83.050003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>88.519997</v>
+        <v>89.480003</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1192.5</v>
+        <v>1198.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>483.25</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2265</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0614</v>
+        <v>6.0196</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4452.100098</v>
+        <v>4451.399902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.050003</v>
+        <v>84.370003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>89.480003</v>
+        <v>91.129997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1198.75</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>486</v>
+        <v>492.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>166934</v>
+        <v>166335</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>163.899994</v>
+        <v>163.800003</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>100.120003</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>458.100006</v>
+        <v>453.890015</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2</v>
+        <v>5.2196</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0196</v>
+        <v>6.0607</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7785.759766</v>
+        <v>7691.759766</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26729.160156</v>
+        <v>26289.710938</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53732.410156</v>
+        <v>53343.398438</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4451.399902</v>
+        <v>4422.299805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>84.370003</v>
+        <v>85.019997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>91.129997</v>
+        <v>92.010002</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1225</v>
+        <v>1227.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>492.75</v>
+        <v>490.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>166335</v>
+        <v>167830</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>163.800003</v>
+        <v>163.550003</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>453.890015</v>
+        <v>453.25</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2196</v>
+        <v>5.1681</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0607</v>
+        <v>6.0502</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7691.759766</v>
+        <v>7707.97998</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26289.710938</v>
+        <v>26331.089844</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53343.398438</v>
+        <v>53463.050781</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4422.299805</v>
+        <v>4543.5</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>85.019997</v>
+        <v>86.589996</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>92.010002</v>
+        <v>93.849998</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1227.25</v>
+        <v>1241.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>490.25</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>167830</v>
+        <v>167927</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>163.550003</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>99</v>
+        <v>99.94000200000001</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>453.25</v>
+        <v>450.299988</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1681</v>
+        <v>5.1931</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0502</v>
+        <v>6.0795</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7707.97998</v>
+        <v>7641.160156</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26331.089844</v>
+        <v>26067.169922</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53463.050781</v>
+        <v>52759.210938</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4543.5</v>
+        <v>4640.700195</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>86.589996</v>
+        <v>87.25</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>93.849998</v>
+        <v>94.05999799999999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1241.5</v>
+        <v>1231.75</v>
       </c>
     </row>
     <row r="15">

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>167927</v>
+        <v>171031.734375</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>99.94000200000001</v>
+        <v>99.25</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>450.299988</v>
+        <v>448</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1931</v>
+        <v>5.1366</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0795</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7641.160156</v>
+        <v>7674.370117</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26067.169922</v>
+        <v>26180.460938</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>52759.210938</v>
+        <v>53277.011719</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4640.700195</v>
+        <v>4624.100098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>87.25</v>
+        <v>87.05999799999999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>94.05999799999999</v>
+        <v>94.389999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1231.75</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>502</v>
+        <v>483.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>165</v>
+        <v>168.330002</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>99.25</v>
+        <v>102.25</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>448</v>
+        <v>445.850006</v>
       </c>
     </row>
     <row r="6">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4624.100098</v>
+        <v>4680.600098</v>
       </c>
     </row>
     <row r="12">
@@ -679,16 +679,16 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>44439</v>
+        <v>46265</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>68.5</v>
+        <v>87.05999799999999</v>
       </c>
       <c r="F12" t="n">
         <v>87.05999799999999</v>
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1225</v>
+        <v>1239.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>483.75</v>
+        <v>508.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>171031.734375</v>
+        <v>170448.875</v>
       </c>
     </row>
     <row r="3">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>5.9925</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4680.600098</v>
+        <v>4700.799805</v>
       </c>
     </row>
     <row r="12">
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46265</v>
+        <v>44439</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>87.05999799999999</v>
+        <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>87.05999799999999</v>
+        <v>85.040001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>94.389999</v>
+        <v>92.779999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1239.5</v>
+        <v>1237.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>508.5</v>
+        <v>522.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>170448.875</v>
+        <v>171907</v>
       </c>
     </row>
     <row r="3">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1366</v>
+        <v>5.154</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9925</v>
+        <v>6.0109</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7674.370117</v>
+        <v>7652.859863</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26180.460938</v>
+        <v>25980.189453</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53277.011719</v>
+        <v>53417.160156</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4700.799805</v>
+        <v>4693.100098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>85.040001</v>
+        <v>82.540001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>92.779999</v>
+        <v>88.019997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1237.25</v>
+        <v>1218.25</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>522.5</v>
+        <v>514.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>171907</v>
+        <v>174577</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>168.330002</v>
+        <v>169.009995</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>102.25</v>
+        <v>102.639999</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>445.850006</v>
+        <v>444.700012</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.154</v>
+        <v>5.148</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0109</v>
+        <v>6.0044</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7652.859863</v>
+        <v>7677.279785</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>25980.189453</v>
+        <v>26151.300781</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53417.160156</v>
+        <v>53577.398438</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4693.100098</v>
+        <v>4670.700195</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>82.540001</v>
+        <v>80.139999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>88.019997</v>
+        <v>84.910004</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1218.25</v>
+        <v>1240.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>514.25</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>174577</v>
+        <v>175329.453125</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>169.009995</v>
+        <v>172.399994</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>102.639999</v>
+        <v>105.360001</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>444.700012</v>
+        <v>450.690002</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.148</v>
+        <v>5.1611</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0044</v>
+        <v>6.013</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7677.279785</v>
+        <v>7730.990234</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26151.300781</v>
+        <v>26541.351562</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53577.398438</v>
+        <v>53569.441406</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4670.700195</v>
+        <v>4660.600098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>80.139999</v>
+        <v>83.639999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>84.910004</v>
+        <v>88.56999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1240.75</v>
+        <v>1263.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>528</v>
+        <v>531.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>175329.453125</v>
+        <v>175664.625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>172.399994</v>
+        <v>172.720001</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>105.360001</v>
+        <v>104.580002</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>450.690002</v>
+        <v>452.049988</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1611</v>
+        <v>5.1925</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.013</v>
+        <v>6.0137</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7730.990234</v>
+        <v>7711.759766</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26541.351562</v>
+        <v>26402.423828</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53569.441406</v>
+        <v>53559.988281</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4660.600098</v>
+        <v>4505.799805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.639999</v>
+        <v>83.400002</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>88.56999999999999</v>
+        <v>88.230003</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1263.5</v>
+        <v>1287.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>531.5</v>
+        <v>536.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>175664.625</v>
+        <v>175135</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>172.720001</v>
+        <v>172.399994</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>104.580002</v>
+        <v>105.169998</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>452.049988</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1925</v>
+        <v>5.2054</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0137</v>
+        <v>6.0054</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7711.759766</v>
+        <v>7730.990234</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26402.423828</v>
+        <v>26541.349609</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53559.988281</v>
+        <v>53569.441406</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4505.799805</v>
+        <v>4609.700195</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.400002</v>
+        <v>83.529999</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>88.230003</v>
+        <v>89.699997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1287.75</v>
+        <v>1256.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>536.25</v>
+        <v>510.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>175135</v>
+        <v>175665</v>
       </c>
     </row>
     <row r="3">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.2054</v>
+        <v>5.185</v>
       </c>
     </row>
     <row r="7">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7730.990234</v>
+        <v>7711.759766</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26541.349609</v>
+        <v>26402.419922</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53569.441406</v>
+        <v>53559.988281</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4609.700195</v>
+        <v>4529.899902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.529999</v>
+        <v>83.400002</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>89.699997</v>
+        <v>88.099998</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1256.5</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>510.25</v>
+        <v>536.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>118781</v>
       </c>
       <c r="F2" t="n">
-        <v>175665</v>
+        <v>177580.765625</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>114.080002</v>
       </c>
       <c r="F3" t="n">
-        <v>172.399994</v>
+        <v>174.800003</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>136.330002</v>
       </c>
       <c r="F4" t="n">
-        <v>105.169998</v>
+        <v>106.550003</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>254</v>
       </c>
       <c r="F5" t="n">
-        <v>450</v>
+        <v>449.230011</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.1829</v>
       </c>
       <c r="F6" t="n">
-        <v>5.185</v>
+        <v>5.1834</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.1119</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0054</v>
+        <v>6.0184</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4522.680176</v>
       </c>
       <c r="F8" t="n">
-        <v>7711.759766</v>
+        <v>7672.839844</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15259.240234</v>
       </c>
       <c r="F9" t="n">
-        <v>26402.419922</v>
+        <v>26289.875</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>35360.730469</v>
       </c>
       <c r="F10" t="n">
-        <v>53559.988281</v>
+        <v>53199.460938</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1815</v>
       </c>
       <c r="F11" t="n">
-        <v>4529.899902</v>
+        <v>4483.399902</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>68.5</v>
       </c>
       <c r="F12" t="n">
-        <v>83.400002</v>
+        <v>85.68000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>72.989998</v>
       </c>
       <c r="F13" t="n">
-        <v>88.099998</v>
+        <v>88.269997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1298.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1288</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>534</v>
       </c>
       <c r="F15" t="n">
-        <v>536.5</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -459,19 +459,19 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D2" t="n">
         <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>118781</v>
+        <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>177580.765625</v>
+        <v>180393.8125</v>
       </c>
     </row>
     <row r="3">
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D3" t="n">
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>114.080002</v>
+        <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>174.800003</v>
+        <v>177.610001</v>
       </c>
     </row>
     <row r="4">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D4" t="n">
         <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>136.330002</v>
+        <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>106.550003</v>
+        <v>108.040001</v>
       </c>
     </row>
     <row r="5">
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D5" t="n">
         <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>449.230011</v>
+        <v>444.790009</v>
       </c>
     </row>
     <row r="6">
@@ -547,19 +547,19 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D6" t="n">
         <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1829</v>
+        <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1834</v>
+        <v>5.1434</v>
       </c>
     </row>
     <row r="7">
@@ -569,19 +569,19 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D7" t="n">
         <v>61</v>
       </c>
       <c r="E7" t="n">
-        <v>6.1119</v>
+        <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0184</v>
+        <v>5.9697</v>
       </c>
     </row>
     <row r="8">
@@ -591,19 +591,19 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D8" t="n">
         <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>4522.680176</v>
+        <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7672.839844</v>
+        <v>7659.640137</v>
       </c>
     </row>
     <row r="9">
@@ -613,19 +613,19 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D9" t="n">
         <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>15259.240234</v>
+        <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26289.875</v>
+        <v>26179.060547</v>
       </c>
     </row>
     <row r="10">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D10" t="n">
         <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>35360.730469</v>
+        <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>53199.460938</v>
+        <v>53141.730469</v>
       </c>
     </row>
     <row r="11">
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D11" t="n">
         <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>1815</v>
+        <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4483.399902</v>
+        <v>4419.100098</v>
       </c>
     </row>
     <row r="12">
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D12" t="n">
         <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>68.5</v>
+        <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>85.68000000000001</v>
+        <v>87.650002</v>
       </c>
     </row>
     <row r="13">
@@ -701,19 +701,19 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
       </c>
       <c r="E13" t="n">
-        <v>72.989998</v>
+        <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>88.269997</v>
+        <v>92.06999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -723,19 +723,19 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>1298.75</v>
+        <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1290</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="15">
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D15" t="n">
         <v>61</v>
       </c>
       <c r="E15" t="n">
-        <v>534</v>
+        <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>538</v>
+        <v>542.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>180393.8125</v>
+        <v>183242.234375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>177.610001</v>
+        <v>180.369995</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>108.040001</v>
+        <v>109.370003</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>444.790009</v>
+        <v>442.920013</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1434</v>
+        <v>5.1304</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9697</v>
+        <v>5.9502</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7659.640137</v>
+        <v>7656.77002</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26179.060547</v>
+        <v>26157.546875</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>53141.730469</v>
+        <v>53092.410156</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4419.100098</v>
+        <v>4431.299805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>87.650002</v>
+        <v>89.129997</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>92.06999999999999</v>
+        <v>93.889999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1312</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>542.25</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>183242.234375</v>
+        <v>187884.234375</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>180.369995</v>
+        <v>184.940002</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>109.370003</v>
+        <v>112.779999</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>442.920013</v>
+        <v>444.200012</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1304</v>
+        <v>5.0978</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9502</v>
+        <v>5.9255</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7656.77002</v>
+        <v>7696.549805</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26157.546875</v>
+        <v>26400.578125</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>53092.410156</v>
+        <v>53321.730469</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4431.299805</v>
+        <v>4514.799805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>89.129997</v>
+        <v>91.870003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>93.889999</v>
+        <v>96.199997</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1304</v>
+        <v>1292.5</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>541</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>187884.234375</v>
+        <v>184429.421875</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>184.940002</v>
+        <v>181.509995</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>112.779999</v>
+        <v>110.269997</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>444.200012</v>
+        <v>447.329987</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0978</v>
+        <v>5.1283</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9255</v>
+        <v>5.9542</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7696.549805</v>
+        <v>7736.689941</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26400.578125</v>
+        <v>26610.115234</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>53321.730469</v>
+        <v>53466.398438</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4514.799805</v>
+        <v>4469.600098</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>91.870003</v>
+        <v>88.91999800000001</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>96.199997</v>
+        <v>93.31999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1292.5</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="15">
@@ -744,21 +744,13 @@
           <t>milho</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>46295</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>61</v>
-      </c>
-      <c r="E15" t="n">
-        <v>536.75</v>
-      </c>
-      <c r="F15" t="n">
-        <v>527</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -471,7 +471,7 @@
         <v>110979</v>
       </c>
       <c r="F2" t="n">
-        <v>184429.421875</v>
+        <v>185147</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>181.509995</v>
+        <v>182.25</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>110.269997</v>
+        <v>111.059998</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>447.329987</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>5.4143</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1283</v>
+        <v>5.1237</v>
       </c>
     </row>
     <row r="7">
@@ -581,7 +581,7 @@
         <v>6.2785</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9542</v>
+        <v>5.9496</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>4307.540039</v>
       </c>
       <c r="F8" t="n">
-        <v>7736.689941</v>
+        <v>7718.600098</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>14448.580078</v>
       </c>
       <c r="F9" t="n">
-        <v>26610.115234</v>
+        <v>26506.990234</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>33843.921875</v>
       </c>
       <c r="F10" t="n">
-        <v>53466.398438</v>
+        <v>53414.25</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4469.600098</v>
+        <v>4429.799805</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +691,7 @@
         <v>75.029999</v>
       </c>
       <c r="F12" t="n">
-        <v>88.91999800000001</v>
+        <v>91.480003</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>78.519997</v>
       </c>
       <c r="F13" t="n">
-        <v>93.31999999999999</v>
+        <v>96.279999</v>
       </c>
     </row>
     <row r="14">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1307</v>
+        <v>1293.75</v>
       </c>
     </row>
     <row r="15">
@@ -744,13 +744,21 @@
           <t>milho</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>46295</v>
+      </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="E15" t="n">
+        <v>536.75</v>
+      </c>
+      <c r="F15" t="n">
+        <v>512</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -493,7 +493,7 @@
         <v>106.489998</v>
       </c>
       <c r="F3" t="n">
-        <v>182.25</v>
+        <v>181.940002</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
         <v>127.400002</v>
       </c>
       <c r="F4" t="n">
-        <v>111.059998</v>
+        <v>110.989998</v>
       </c>
     </row>
     <row r="5">
@@ -537,7 +537,7 @@
         <v>255</v>
       </c>
       <c r="F5" t="n">
-        <v>446</v>
+        <v>447.350006</v>
       </c>
     </row>
     <row r="6">

--- a/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
+++ b/data/final/yahoo/resumo_disponibilidade_yahoo.xlsx
@@ -669,7 +669,7 @@
         <v>1755.300049</v>
       </c>
       <c r="F11" t="n">
-        <v>4429.799805</v>
+        <v>4476.600098</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +735,7 @@
         <v>1256</v>
       </c>
       <c r="F14" t="n">
-        <v>1293.75</v>
+        <v>1309.75</v>
       </c>
     </row>
     <row r="15">
@@ -757,7 +757,7 @@
         <v>536.75</v>
       </c>
       <c r="F15" t="n">
-        <v>512</v>
+        <v>536.75</v>
       </c>
     </row>
   </sheetData>
